--- a/artfynd/A 30663-2026 artfynd.xlsx
+++ b/artfynd/A 30663-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420642</v>
       </c>
       <c r="B2" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136420658</v>
       </c>
       <c r="B3" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136420758</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136420608</v>
       </c>
       <c r="B5" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136420589</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2026 artfynd.xlsx
+++ b/artfynd/A 30663-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420642</v>
       </c>
       <c r="B2" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136420658</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136420758</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2026 artfynd.xlsx
+++ b/artfynd/A 30663-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420642</v>
       </c>
       <c r="B2" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136420658</v>
       </c>
       <c r="B3" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136420758</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30663-2026 artfynd.xlsx
+++ b/artfynd/A 30663-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420642</v>
       </c>
       <c r="B2" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136420658</v>
       </c>
       <c r="B3" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136420758</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
